--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/29.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/29.xlsx
@@ -426,13 +426,13 @@
         <v>-22.27969329289469</v>
       </c>
       <c r="E2">
-        <v>-27.28345710469085</v>
+        <v>-31.04086946686889</v>
       </c>
       <c r="F2">
-        <v>-3.583907692804888</v>
+        <v>-3.931999272604879</v>
       </c>
       <c r="G2">
-        <v>-16.12116455383408</v>
+        <v>-17.18413443559503</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-21.60096667860115</v>
       </c>
       <c r="E3">
-        <v>-27.7515032549424</v>
+        <v>-31.30094978984664</v>
       </c>
       <c r="F3">
-        <v>-3.564401297203765</v>
+        <v>-3.821276372077086</v>
       </c>
       <c r="G3">
-        <v>-15.23408053517642</v>
+        <v>-16.77017346785582</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-20.6291866210478</v>
       </c>
       <c r="E4">
-        <v>-28.56381532172598</v>
+        <v>-31.69337842150704</v>
       </c>
       <c r="F4">
-        <v>-3.341337694610511</v>
+        <v>-3.850547562622409</v>
       </c>
       <c r="G4">
-        <v>-15.81459003798883</v>
+        <v>-16.65165088490846</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-19.44894026547754</v>
       </c>
       <c r="E5">
-        <v>-29.38857663945573</v>
+        <v>-31.50963412267964</v>
       </c>
       <c r="F5">
-        <v>-3.290639124456973</v>
+        <v>-3.912335487197224</v>
       </c>
       <c r="G5">
-        <v>-15.58109809548261</v>
+        <v>-16.64578976330141</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-18.08500948564831</v>
       </c>
       <c r="E6">
-        <v>-28.19458445192041</v>
+        <v>-31.86589866672909</v>
       </c>
       <c r="F6">
-        <v>-3.610461009901626</v>
+        <v>-3.835678367742158</v>
       </c>
       <c r="G6">
-        <v>-14.96381494973208</v>
+        <v>-16.92377662587397</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.61890813627049</v>
       </c>
       <c r="E7">
-        <v>-28.64672380279787</v>
+        <v>-32.43122340923644</v>
       </c>
       <c r="F7">
-        <v>-3.835134130358519</v>
+        <v>-3.892660933013333</v>
       </c>
       <c r="G7">
-        <v>-15.12492269307739</v>
+        <v>-16.15245432775857</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-15.08919472964013</v>
       </c>
       <c r="E8">
-        <v>-29.60442110861273</v>
+        <v>-32.67535332412119</v>
       </c>
       <c r="F8">
-        <v>-3.443137421475348</v>
+        <v>-3.835413290173262</v>
       </c>
       <c r="G8">
-        <v>-14.5733741800142</v>
+        <v>-16.30772444619815</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-13.56570140185242</v>
       </c>
       <c r="E9">
-        <v>-29.10642199828651</v>
+        <v>-33.23078719385845</v>
       </c>
       <c r="F9">
-        <v>-2.893349147869913</v>
+        <v>-3.635366704234196</v>
       </c>
       <c r="G9">
-        <v>-14.74895850211723</v>
+        <v>-16.05428772038812</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-12.08744217709046</v>
       </c>
       <c r="E10">
-        <v>-29.67006261360164</v>
+        <v>-33.25720161788437</v>
       </c>
       <c r="F10">
-        <v>-3.43564566668443</v>
+        <v>-3.817959588996277</v>
       </c>
       <c r="G10">
-        <v>-14.24050163390267</v>
+        <v>-15.57983057898363</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.69576473752897</v>
       </c>
       <c r="E11">
-        <v>-30.41831554891106</v>
+        <v>-34.32567129954939</v>
       </c>
       <c r="F11">
-        <v>-3.121749093272002</v>
+        <v>-3.639332098991397</v>
       </c>
       <c r="G11">
-        <v>-14.1738924017773</v>
+        <v>-15.4848882411832</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.424838441835931</v>
       </c>
       <c r="E12">
-        <v>-30.91741733684403</v>
+        <v>-34.63516237765863</v>
       </c>
       <c r="F12">
-        <v>-3.03460981270191</v>
+        <v>-3.620436210166138</v>
       </c>
       <c r="G12">
-        <v>-13.52779838409154</v>
+        <v>-15.06603082196335</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.278485592610364</v>
       </c>
       <c r="E13">
-        <v>-31.70714424044318</v>
+        <v>-34.86105761822171</v>
       </c>
       <c r="F13">
-        <v>-3.292845066850628</v>
+        <v>-3.603196227779074</v>
       </c>
       <c r="G13">
-        <v>-13.10333961235145</v>
+        <v>-14.84882731496109</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.282741918006297</v>
       </c>
       <c r="E14">
-        <v>-32.96431300204613</v>
+        <v>-34.84054698409405</v>
       </c>
       <c r="F14">
-        <v>-2.932154847221459</v>
+        <v>-3.367996214367405</v>
       </c>
       <c r="G14">
-        <v>-12.66717295649252</v>
+        <v>-14.43768725675257</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.422582562094034</v>
       </c>
       <c r="E15">
-        <v>-32.04785916129248</v>
+        <v>-35.7762613423666</v>
       </c>
       <c r="F15">
-        <v>-3.532027042367555</v>
+        <v>-3.300851237798685</v>
       </c>
       <c r="G15">
-        <v>-12.17774450023029</v>
+        <v>-14.35951112071627</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.698265099900949</v>
       </c>
       <c r="E16">
-        <v>-32.76317505419035</v>
+        <v>-36.34301063635836</v>
       </c>
       <c r="F16">
-        <v>-2.984062833783085</v>
+        <v>-3.360033118524293</v>
       </c>
       <c r="G16">
-        <v>-11.90199374040002</v>
+        <v>-14.00972356039891</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.088166156810828</v>
       </c>
       <c r="E17">
-        <v>-34.48077712968644</v>
+        <v>-36.69002390218176</v>
       </c>
       <c r="F17">
-        <v>-2.939133014222642</v>
+        <v>-3.298506958048763</v>
       </c>
       <c r="G17">
-        <v>-11.72482339095789</v>
+        <v>-13.73254080716042</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.568864463868957</v>
       </c>
       <c r="E18">
-        <v>-34.06256951533283</v>
+        <v>-37.67153156852186</v>
       </c>
       <c r="F18">
-        <v>-2.634267302235534</v>
+        <v>-3.222026280850493</v>
       </c>
       <c r="G18">
-        <v>-11.69796143985992</v>
+        <v>-13.48133757334809</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.121388093558892</v>
       </c>
       <c r="E19">
-        <v>-34.47464491316533</v>
+        <v>-37.91415802090702</v>
       </c>
       <c r="F19">
-        <v>-2.301104559768796</v>
+        <v>-2.93015185484149</v>
       </c>
       <c r="G19">
-        <v>-10.55918336740681</v>
+        <v>-12.98728418304269</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.71172819574913</v>
       </c>
       <c r="E20">
-        <v>-34.8910977957342</v>
+        <v>-38.27479381987586</v>
       </c>
       <c r="F20">
-        <v>-2.173352910541653</v>
+        <v>-2.998831796207597</v>
       </c>
       <c r="G20">
-        <v>-11.00259353413378</v>
+        <v>-12.74485957791798</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.330185584015559</v>
       </c>
       <c r="E21">
-        <v>-35.80143603281204</v>
+        <v>-38.80100984794296</v>
       </c>
       <c r="F21">
-        <v>-2.13865508514059</v>
+        <v>-2.986346642712603</v>
       </c>
       <c r="G21">
-        <v>-10.34970113753277</v>
+        <v>-12.81623341892213</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.956281660988962</v>
       </c>
       <c r="E22">
-        <v>-36.42243457312872</v>
+        <v>-39.3965014409082</v>
       </c>
       <c r="F22">
-        <v>-2.166341608844358</v>
+        <v>-2.663994094852397</v>
       </c>
       <c r="G22">
-        <v>-10.12871205087339</v>
+        <v>-12.33059967992308</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.589854486706171</v>
       </c>
       <c r="E23">
-        <v>-35.83581008634199</v>
+        <v>-39.57670097386986</v>
       </c>
       <c r="F23">
-        <v>-1.94861766252955</v>
+        <v>-2.773577990201341</v>
       </c>
       <c r="G23">
-        <v>-10.61691998403928</v>
+        <v>-12.4615924844099</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.23311520649098</v>
       </c>
       <c r="E24">
-        <v>-36.55679095948692</v>
+        <v>-40.32636600102973</v>
       </c>
       <c r="F24">
-        <v>-1.892315186896073</v>
+        <v>-2.501868511878687</v>
       </c>
       <c r="G24">
-        <v>-10.73179274604826</v>
+        <v>-12.15539522115806</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.89566004977981</v>
       </c>
       <c r="E25">
-        <v>-38.44688420772579</v>
+        <v>-39.90672345216339</v>
       </c>
       <c r="F25">
-        <v>-2.096287405957006</v>
+        <v>-2.495020398559743</v>
       </c>
       <c r="G25">
-        <v>-11.18204828509314</v>
+        <v>-12.27675307273137</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.594345053697666</v>
       </c>
       <c r="E26">
-        <v>-36.36777208227699</v>
+        <v>-40.05611446351747</v>
       </c>
       <c r="F26">
-        <v>-2.618126563391986</v>
+        <v>-2.574527930247843</v>
       </c>
       <c r="G26">
-        <v>-10.84879718101589</v>
+        <v>-12.02549370791033</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.341977173068065</v>
       </c>
       <c r="E27">
-        <v>-36.9458284941006</v>
+        <v>-40.22965224551411</v>
       </c>
       <c r="F27">
-        <v>-2.142780354806532</v>
+        <v>-2.443880308580513</v>
       </c>
       <c r="G27">
-        <v>-10.565385191183</v>
+        <v>-12.20283506112318</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.15657167872916</v>
       </c>
       <c r="E28">
-        <v>-37.48865321425569</v>
+        <v>-40.14890966414811</v>
       </c>
       <c r="F28">
-        <v>-2.049863211601914</v>
+        <v>-2.50268611050525</v>
       </c>
       <c r="G28">
-        <v>-10.5076263832215</v>
+        <v>-12.40337549077266</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.046088172185728</v>
       </c>
       <c r="E29">
-        <v>-38.23606512427183</v>
+        <v>-40.58110944745508</v>
       </c>
       <c r="F29">
-        <v>-2.137118463608397</v>
+        <v>-2.47810016599016</v>
       </c>
       <c r="G29">
-        <v>-10.60270709048526</v>
+        <v>-12.14523289783715</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.016516630495495</v>
       </c>
       <c r="E30">
-        <v>-36.29585507497626</v>
+        <v>-39.93692768152321</v>
       </c>
       <c r="F30">
-        <v>-2.119547134260214</v>
+        <v>-2.37345582546411</v>
       </c>
       <c r="G30">
-        <v>-10.86676693603652</v>
+        <v>-12.31567666384028</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.063280480659754</v>
       </c>
       <c r="E31">
-        <v>-36.6815908065867</v>
+        <v>-40.07873700560381</v>
       </c>
       <c r="F31">
-        <v>-1.959507380406752</v>
+        <v>-2.49344235865741</v>
       </c>
       <c r="G31">
-        <v>-10.92482336888141</v>
+        <v>-12.33897755931597</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.176100552353518</v>
       </c>
       <c r="E32">
-        <v>-36.81872569132121</v>
+        <v>-39.63052243942832</v>
       </c>
       <c r="F32">
-        <v>-2.068992700034763</v>
+        <v>-2.387392278648809</v>
       </c>
       <c r="G32">
-        <v>-11.13375081552984</v>
+        <v>-12.39627296011254</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.337965958445573</v>
       </c>
       <c r="E33">
-        <v>-37.44498635038644</v>
+        <v>-39.66822736844077</v>
       </c>
       <c r="F33">
-        <v>-1.985198367037176</v>
+        <v>-2.408104777188408</v>
       </c>
       <c r="G33">
-        <v>-10.97481129556745</v>
+        <v>-12.49481290395952</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.527868276348614</v>
       </c>
       <c r="E34">
-        <v>-35.32033426276089</v>
+        <v>-38.8652579505324</v>
       </c>
       <c r="F34">
-        <v>-1.618370773320665</v>
+        <v>-2.440724228775847</v>
       </c>
       <c r="G34">
-        <v>-11.02827281793197</v>
+        <v>-12.34277097120685</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.724929889181425</v>
       </c>
       <c r="E35">
-        <v>-35.44283530739237</v>
+        <v>-38.28409701324347</v>
       </c>
       <c r="F35">
-        <v>-2.176209121346506</v>
+        <v>-2.480579469626739</v>
       </c>
       <c r="G35">
-        <v>-10.54409848515936</v>
+        <v>-12.76385535556292</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.909269803193101</v>
       </c>
       <c r="E36">
-        <v>-35.49956609748387</v>
+        <v>-38.47431824513195</v>
       </c>
       <c r="F36">
-        <v>-1.74383281504647</v>
+        <v>-2.520300514958378</v>
       </c>
       <c r="G36">
-        <v>-10.44501420106513</v>
+        <v>-12.78562113321904</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.067637472356346</v>
       </c>
       <c r="E37">
-        <v>-34.88770877529314</v>
+        <v>-38.09577379893045</v>
       </c>
       <c r="F37">
-        <v>-1.799303609807536</v>
+        <v>-2.379553437916117</v>
       </c>
       <c r="G37">
-        <v>-11.79339720838807</v>
+        <v>-12.58948633506706</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.191281850762748</v>
       </c>
       <c r="E38">
-        <v>-35.32958969419828</v>
+        <v>-37.86654975949052</v>
       </c>
       <c r="F38">
-        <v>-1.762272273432787</v>
+        <v>-2.471075610414421</v>
       </c>
       <c r="G38">
-        <v>-11.21064899208878</v>
+        <v>-13.04870586566552</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.280906421810459</v>
       </c>
       <c r="E39">
-        <v>-34.25362969590892</v>
+        <v>-37.21765617531063</v>
       </c>
       <c r="F39">
-        <v>-2.530153116847276</v>
+        <v>-2.43990248831227</v>
       </c>
       <c r="G39">
-        <v>-11.21355736156328</v>
+        <v>-12.86796010150586</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.34005979797643</v>
       </c>
       <c r="E40">
-        <v>-33.69202000093163</v>
+        <v>-37.10383949555936</v>
       </c>
       <c r="F40">
-        <v>-2.02688844168527</v>
+        <v>-2.399162551075187</v>
       </c>
       <c r="G40">
-        <v>-11.93264257652739</v>
+        <v>-13.2050920774178</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.378266115338998</v>
       </c>
       <c r="E41">
-        <v>-34.03383136957068</v>
+        <v>-36.45121840421545</v>
       </c>
       <c r="F41">
-        <v>-1.62114746085485</v>
+        <v>-2.321020997234304</v>
       </c>
       <c r="G41">
-        <v>-11.73974901778528</v>
+        <v>-13.00255312278382</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.404096597333201</v>
       </c>
       <c r="E42">
-        <v>-32.99678073157798</v>
+        <v>-36.21062287216813</v>
       </c>
       <c r="F42">
-        <v>-1.388754784571268</v>
+        <v>-2.289477594903102</v>
       </c>
       <c r="G42">
-        <v>-10.97466770461494</v>
+        <v>-13.07852709575751</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.426139186153838</v>
       </c>
       <c r="E43">
-        <v>-33.18491497477573</v>
+        <v>-35.69559559541011</v>
       </c>
       <c r="F43">
-        <v>-1.477629494850224</v>
+        <v>-2.183713301648467</v>
       </c>
       <c r="G43">
-        <v>-11.45554858308587</v>
+        <v>-13.3328566962177</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.452765399132915</v>
       </c>
       <c r="E44">
-        <v>-32.09208878529624</v>
+        <v>-35.48332911780945</v>
       </c>
       <c r="F44">
-        <v>-1.624611693333357</v>
+        <v>-2.186092372829306</v>
       </c>
       <c r="G44">
-        <v>-11.35697208881462</v>
+        <v>-13.42314538178447</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.48671393328243</v>
       </c>
       <c r="E45">
-        <v>-32.24169784024487</v>
+        <v>-35.29420018049941</v>
       </c>
       <c r="F45">
-        <v>-1.898652197527489</v>
+        <v>-1.982052227641344</v>
       </c>
       <c r="G45">
-        <v>-11.29518229120444</v>
+        <v>-13.52270221064969</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.531143324842869</v>
       </c>
       <c r="E46">
-        <v>-31.42529278370068</v>
+        <v>-34.28252774030707</v>
       </c>
       <c r="F46">
-        <v>-1.608937325337585</v>
+        <v>-2.14088007998451</v>
       </c>
       <c r="G46">
-        <v>-11.62737604372229</v>
+        <v>-13.48009746966731</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.584676780536879</v>
       </c>
       <c r="E47">
-        <v>-32.1837999977711</v>
+        <v>-34.75902982881598</v>
       </c>
       <c r="F47">
-        <v>-1.674114100957253</v>
+        <v>-1.90556740860606</v>
       </c>
       <c r="G47">
-        <v>-12.01118291143415</v>
+        <v>-13.61264627793043</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.648828689417734</v>
       </c>
       <c r="E48">
-        <v>-30.13458268743842</v>
+        <v>-34.21741784636774</v>
       </c>
       <c r="F48">
-        <v>-1.836020994936624</v>
+        <v>-1.832714152264649</v>
       </c>
       <c r="G48">
-        <v>-12.19463471236249</v>
+        <v>-13.53866169233516</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.724092500644213</v>
       </c>
       <c r="E49">
-        <v>-30.22769353212975</v>
+        <v>-33.88164524699499</v>
       </c>
       <c r="F49">
-        <v>-1.939461717626407</v>
+        <v>-1.844478626119207</v>
       </c>
       <c r="G49">
-        <v>-11.85785649234265</v>
+        <v>-13.56739293656036</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.810093396692084</v>
       </c>
       <c r="E50">
-        <v>-30.63203980368674</v>
+        <v>-33.41745535345854</v>
       </c>
       <c r="F50">
-        <v>-1.45792760454204</v>
+        <v>-1.966076333910952</v>
       </c>
       <c r="G50">
-        <v>-11.9740346266472</v>
+        <v>-13.67910147612492</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.910107142860635</v>
       </c>
       <c r="E51">
-        <v>-28.65103483615304</v>
+        <v>-32.71743158465869</v>
       </c>
       <c r="F51">
-        <v>-1.558932927067592</v>
+        <v>-2.007758124885018</v>
       </c>
       <c r="G51">
-        <v>-11.499578790615</v>
+        <v>-13.86814027047825</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.024044979336158</v>
       </c>
       <c r="E52">
-        <v>-29.14469591725047</v>
+        <v>-32.7184698874899</v>
       </c>
       <c r="F52">
-        <v>-1.792527564452636</v>
+        <v>-1.817543431649778</v>
       </c>
       <c r="G52">
-        <v>-11.64614207584321</v>
+        <v>-13.67389173529335</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.157503744708776</v>
       </c>
       <c r="E53">
-        <v>-28.94072340266549</v>
+        <v>-31.78267661820218</v>
       </c>
       <c r="F53">
-        <v>-1.606173063314443</v>
+        <v>-1.748701130272723</v>
       </c>
       <c r="G53">
-        <v>-12.14998445299298</v>
+        <v>-13.89000525642882</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.311434172006686</v>
       </c>
       <c r="E54">
-        <v>-28.25494722531547</v>
+        <v>-31.49790960710965</v>
       </c>
       <c r="F54">
-        <v>-1.172185582415962</v>
+        <v>-2.061070194194389</v>
       </c>
       <c r="G54">
-        <v>-11.8835775480543</v>
+        <v>-13.72378436980182</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.490673521399211</v>
       </c>
       <c r="E55">
-        <v>-28.24045044118615</v>
+        <v>-31.49198089794345</v>
       </c>
       <c r="F55">
-        <v>-1.442746115150934</v>
+        <v>-1.96396896723823</v>
       </c>
       <c r="G55">
-        <v>-12.33778836515472</v>
+        <v>-13.96855081282476</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.697262572003544</v>
       </c>
       <c r="E56">
-        <v>-28.05199640071639</v>
+        <v>-31.1174339176421</v>
       </c>
       <c r="F56">
-        <v>-1.445947755162754</v>
+        <v>-1.962048811598541</v>
       </c>
       <c r="G56">
-        <v>-12.36107490153515</v>
+        <v>-13.91874955437698</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.930163268875245</v>
       </c>
       <c r="E57">
-        <v>-28.38863079143904</v>
+        <v>-30.42649945182664</v>
       </c>
       <c r="F57">
-        <v>-1.849087662348384</v>
+        <v>-1.904486389145406</v>
       </c>
       <c r="G57">
-        <v>-12.89100122789473</v>
+        <v>-14.44345569692663</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.191532687083344</v>
       </c>
       <c r="E58">
-        <v>-27.51627782513808</v>
+        <v>-30.69104032376726</v>
       </c>
       <c r="F58">
-        <v>-2.002677747603649</v>
+        <v>-1.998549992835499</v>
       </c>
       <c r="G58">
-        <v>-12.56793072235053</v>
+        <v>-14.15382621885</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.475351789570345</v>
       </c>
       <c r="E59">
-        <v>-27.91667646933083</v>
+        <v>-29.9521985653199</v>
       </c>
       <c r="F59">
-        <v>-1.817160725909685</v>
+        <v>-1.96559339571512</v>
       </c>
       <c r="G59">
-        <v>-12.37440666878967</v>
+        <v>-14.43989333593206</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.782057401312082</v>
       </c>
       <c r="E60">
-        <v>-26.78131308946245</v>
+        <v>-29.91731782000832</v>
       </c>
       <c r="F60">
-        <v>-1.829662446752735</v>
+        <v>-1.987444071066166</v>
       </c>
       <c r="G60">
-        <v>-12.41997460488296</v>
+        <v>-14.32307948531958</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.104064667970209</v>
       </c>
       <c r="E61">
-        <v>-25.72298347324699</v>
+        <v>-29.69642304588033</v>
       </c>
       <c r="F61">
-        <v>-1.659064321983191</v>
+        <v>-2.344684968830077</v>
       </c>
       <c r="G61">
-        <v>-12.05578487202873</v>
+        <v>-14.26656600252805</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.438508172215602</v>
       </c>
       <c r="E62">
-        <v>-26.18226634760316</v>
+        <v>-29.09959204226283</v>
       </c>
       <c r="F62">
-        <v>-1.881843794557285</v>
+        <v>-2.35916980123543</v>
       </c>
       <c r="G62">
-        <v>-12.441673808552</v>
+        <v>-14.66531024541796</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.780737951954906</v>
       </c>
       <c r="E63">
-        <v>-27.40422003038288</v>
+        <v>-29.07314231594066</v>
       </c>
       <c r="F63">
-        <v>-1.914732465550633</v>
+        <v>-2.336061664166935</v>
       </c>
       <c r="G63">
-        <v>-13.00288990883607</v>
+        <v>-14.89745634908746</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.123296401549438</v>
       </c>
       <c r="E64">
-        <v>-25.56743324949819</v>
+        <v>-28.79584070220451</v>
       </c>
       <c r="F64">
-        <v>-1.894262678660055</v>
+        <v>-2.387394763751017</v>
       </c>
       <c r="G64">
-        <v>-13.2520084630924</v>
+        <v>-14.76654708842756</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.465767664150587</v>
       </c>
       <c r="E65">
-        <v>-26.35581243602244</v>
+        <v>-29.1854243841074</v>
       </c>
       <c r="F65">
-        <v>-1.742272999226999</v>
+        <v>-2.405061355350522</v>
       </c>
       <c r="G65">
-        <v>-12.63015912505201</v>
+        <v>-14.81094280019944</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.799366189285803</v>
       </c>
       <c r="E66">
-        <v>-26.05384905343946</v>
+        <v>-28.97586995350185</v>
       </c>
       <c r="F66">
-        <v>-2.042530503352333</v>
+        <v>-2.512696102200679</v>
       </c>
       <c r="G66">
-        <v>-12.86141104869905</v>
+        <v>-14.90197946409156</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.125667613762898</v>
       </c>
       <c r="E67">
-        <v>-24.49764492323753</v>
+        <v>-28.96778365105241</v>
       </c>
       <c r="F67">
-        <v>-1.598282035435375</v>
+        <v>-2.699089536606804</v>
       </c>
       <c r="G67">
-        <v>-13.0955713418206</v>
+        <v>-14.84334214057516</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.439803051382906</v>
       </c>
       <c r="E68">
-        <v>-26.21239374255346</v>
+        <v>-28.67870768321037</v>
       </c>
       <c r="F68">
-        <v>-2.017332395326575</v>
+        <v>-2.624668180771894</v>
       </c>
       <c r="G68">
-        <v>-13.12863903281164</v>
+        <v>-14.61274551382049</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.741311267261068</v>
       </c>
       <c r="E69">
-        <v>-25.97066438381447</v>
+        <v>-28.74145024669455</v>
       </c>
       <c r="F69">
-        <v>-2.150339207357077</v>
+        <v>-2.780884190694033</v>
       </c>
       <c r="G69">
-        <v>-13.36761614970378</v>
+        <v>-14.62116385975453</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.030798128206026</v>
       </c>
       <c r="E70">
-        <v>-25.77453728542209</v>
+        <v>-28.72847146130447</v>
       </c>
       <c r="F70">
-        <v>-2.366315298451978</v>
+        <v>-2.671645724552056</v>
       </c>
       <c r="G70">
-        <v>-13.21484973532709</v>
+        <v>-14.57571210179555</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.304263603034759</v>
       </c>
       <c r="E71">
-        <v>-25.09839032852868</v>
+        <v>-28.62920140421841</v>
       </c>
       <c r="F71">
-        <v>-2.105552695357319</v>
+        <v>-2.963559912196394</v>
       </c>
       <c r="G71">
-        <v>-12.33448446787466</v>
+        <v>-14.49612355293546</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.566021875675325</v>
       </c>
       <c r="E72">
-        <v>-25.73482012552275</v>
+        <v>-28.36763630819204</v>
       </c>
       <c r="F72">
-        <v>-2.725743914526684</v>
+        <v>-2.955004533660281</v>
       </c>
       <c r="G72">
-        <v>-12.85822332955331</v>
+        <v>-14.6203493074421</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.810309386901473</v>
       </c>
       <c r="E73">
-        <v>-24.61562104413061</v>
+        <v>-28.54210440952544</v>
       </c>
       <c r="F73">
-        <v>-2.766848333420998</v>
+        <v>-3.030139113829001</v>
       </c>
       <c r="G73">
-        <v>-12.67921893203592</v>
+        <v>-14.40765586172099</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.039050888539652</v>
       </c>
       <c r="E74">
-        <v>-25.533829616669</v>
+        <v>-28.78594775282877</v>
       </c>
       <c r="F74">
-        <v>-2.471511331668293</v>
+        <v>-3.168994199723268</v>
       </c>
       <c r="G74">
-        <v>-12.71929908299869</v>
+        <v>-14.3615892734108</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.249803022925731</v>
       </c>
       <c r="E75">
-        <v>-25.91702981276563</v>
+        <v>-28.89380872754023</v>
       </c>
       <c r="F75">
-        <v>-2.645573688916345</v>
+        <v>-3.00434540964063</v>
       </c>
       <c r="G75">
-        <v>-12.23360790761863</v>
+        <v>-14.13493356561641</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.439219941597614</v>
       </c>
       <c r="E76">
-        <v>-27.00197736036192</v>
+        <v>-29.4878176240625</v>
       </c>
       <c r="F76">
-        <v>-2.446349671808258</v>
+        <v>-3.073755142688604</v>
       </c>
       <c r="G76">
-        <v>-11.87480805697275</v>
+        <v>-14.06359366429195</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.607489978962109</v>
       </c>
       <c r="E77">
-        <v>-25.3957104208505</v>
+        <v>-28.94820541286717</v>
       </c>
       <c r="F77">
-        <v>-2.399025870453725</v>
+        <v>-3.09705877446416</v>
       </c>
       <c r="G77">
-        <v>-11.84982453660809</v>
+        <v>-13.96115718414273</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.747149560550511</v>
       </c>
       <c r="E78">
-        <v>-26.64317728079865</v>
+        <v>-29.32264233306841</v>
       </c>
       <c r="F78">
-        <v>-2.515843069963914</v>
+        <v>-3.267892155576098</v>
       </c>
       <c r="G78">
-        <v>-12.49982292282986</v>
+        <v>-14.08591291980137</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.856599672898028</v>
       </c>
       <c r="E79">
-        <v>-27.21705556202949</v>
+        <v>-29.95468633890347</v>
       </c>
       <c r="F79">
-        <v>-2.952043120195272</v>
+        <v>-3.182609246355681</v>
       </c>
       <c r="G79">
-        <v>-11.93609006475996</v>
+        <v>-13.67841746104205</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-9.927313928968111</v>
       </c>
       <c r="E80">
-        <v>-27.84108387000763</v>
+        <v>-30.41039952812594</v>
       </c>
       <c r="F80">
-        <v>-2.960557908728648</v>
+        <v>-3.436513795722563</v>
       </c>
       <c r="G80">
-        <v>-11.79145089829539</v>
+        <v>-13.45643890218264</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.951771836233641</v>
       </c>
       <c r="E81">
-        <v>-26.73622167410879</v>
+        <v>-30.41350613019691</v>
       </c>
       <c r="F81">
-        <v>-2.975909213437329</v>
+        <v>-3.371123301312973</v>
       </c>
       <c r="G81">
-        <v>-11.88532935767494</v>
+        <v>-13.39378886422969</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.924783702291524</v>
       </c>
       <c r="E82">
-        <v>-28.17088415149527</v>
+        <v>-30.84836604535742</v>
       </c>
       <c r="F82">
-        <v>-2.949538965536609</v>
+        <v>-3.42056689485127</v>
       </c>
       <c r="G82">
-        <v>-11.68592851803948</v>
+        <v>-13.11035729381237</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.835009122734267</v>
       </c>
       <c r="E83">
-        <v>-27.86360673502217</v>
+        <v>-31.63430314362268</v>
       </c>
       <c r="F83">
-        <v>-2.789731982923334</v>
+        <v>-3.358933046613375</v>
       </c>
       <c r="G83">
-        <v>-11.78864434785994</v>
+        <v>-12.91993611019804</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.679219827712185</v>
       </c>
       <c r="E84">
-        <v>-29.44703101224703</v>
+        <v>-32.08341895665566</v>
       </c>
       <c r="F84">
-        <v>-3.003237882423087</v>
+        <v>-3.367688890060966</v>
       </c>
       <c r="G84">
-        <v>-12.12451794487897</v>
+        <v>-13.18977353352944</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.450784616235968</v>
       </c>
       <c r="E85">
-        <v>-30.1168484750814</v>
+        <v>-32.56683821862607</v>
       </c>
       <c r="F85">
-        <v>-2.710127532249107</v>
+        <v>-3.266107023823066</v>
       </c>
       <c r="G85">
-        <v>-11.01720848235484</v>
+        <v>-12.84433286295629</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.147770221056422</v>
       </c>
       <c r="E86">
-        <v>-30.4062525466181</v>
+        <v>-33.13205290103331</v>
       </c>
       <c r="F86">
-        <v>-3.321127186717009</v>
+        <v>-3.426102045836776</v>
       </c>
       <c r="G86">
-        <v>-10.66530360817409</v>
+        <v>-12.56937576948171</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.774367571528531</v>
       </c>
       <c r="E87">
-        <v>-30.94049257896477</v>
+        <v>-33.95179090966568</v>
       </c>
       <c r="F87">
-        <v>-2.888232322422821</v>
+        <v>-3.485413151877221</v>
       </c>
       <c r="G87">
-        <v>-10.98648654537891</v>
+        <v>-12.73389183989072</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.330388345072935</v>
       </c>
       <c r="E88">
-        <v>-32.37963014155376</v>
+        <v>-34.61028048861158</v>
       </c>
       <c r="F88">
-        <v>-3.214159275626106</v>
+        <v>-3.465562155436533</v>
       </c>
       <c r="G88">
-        <v>-10.27607683469108</v>
+        <v>-12.52457278155362</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.829035797411809</v>
       </c>
       <c r="E89">
-        <v>-33.17497634007541</v>
+        <v>-35.75060695601313</v>
       </c>
       <c r="F89">
-        <v>-3.283013174146801</v>
+        <v>-3.757931116785008</v>
       </c>
       <c r="G89">
-        <v>-10.7729406915488</v>
+        <v>-12.59677031247626</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.274916941137688</v>
       </c>
       <c r="E90">
-        <v>-33.79988720546007</v>
+        <v>-36.27862755440087</v>
       </c>
       <c r="F90">
-        <v>-3.603493611676679</v>
+        <v>-3.679299169441668</v>
       </c>
       <c r="G90">
-        <v>-10.07365666893599</v>
+        <v>-12.41265016093259</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.681077024549776</v>
       </c>
       <c r="E91">
-        <v>-34.67431677742345</v>
+        <v>-37.49203808148543</v>
       </c>
       <c r="F91">
-        <v>-3.489743856659056</v>
+        <v>-3.922787827085748</v>
       </c>
       <c r="G91">
-        <v>-11.31855367678409</v>
+        <v>-12.70321428557284</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.058641796213567</v>
       </c>
       <c r="E92">
-        <v>-36.15072941165278</v>
+        <v>-38.28030513130391</v>
       </c>
       <c r="F92">
-        <v>-3.824503691478393</v>
+        <v>-4.018143683924208</v>
       </c>
       <c r="G92">
-        <v>-11.31974678706223</v>
+        <v>-12.40708274809204</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.412760175485363</v>
       </c>
       <c r="E93">
-        <v>-36.47853407509884</v>
+        <v>-39.5546931070596</v>
       </c>
       <c r="F93">
-        <v>-3.582343735148402</v>
+        <v>-3.981176131839474</v>
       </c>
       <c r="G93">
-        <v>-11.37719100030049</v>
+        <v>-12.54627329059495</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.758786664606731</v>
       </c>
       <c r="E94">
-        <v>-37.98562648138468</v>
+        <v>-40.69433844780387</v>
       </c>
       <c r="F94">
-        <v>-3.63355423635687</v>
+        <v>-3.956898339998227</v>
       </c>
       <c r="G94">
-        <v>-11.60833979953618</v>
+        <v>-12.50992128290829</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.096388814269654</v>
       </c>
       <c r="E95">
-        <v>-40.77596150997073</v>
+        <v>-42.69800125972018</v>
       </c>
       <c r="F95">
-        <v>-3.601572627669587</v>
+        <v>-3.976462721317545</v>
       </c>
       <c r="G95">
-        <v>-11.22086222492922</v>
+        <v>-12.93318563899794</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.434435837044141</v>
       </c>
       <c r="E96">
-        <v>-42.28827450289187</v>
+        <v>-43.5239026339586</v>
       </c>
       <c r="F96">
-        <v>-4.347337718164134</v>
+        <v>-4.221925378482497</v>
       </c>
       <c r="G96">
-        <v>-11.61651404085096</v>
+        <v>-12.9784402857403</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.77529704062582</v>
       </c>
       <c r="E97">
-        <v>-42.55794459081865</v>
+        <v>-45.08889703592953</v>
       </c>
       <c r="F97">
-        <v>-4.060152680022379</v>
+        <v>-4.347214291421118</v>
       </c>
       <c r="G97">
-        <v>-12.17393020238267</v>
+        <v>-13.04208893349935</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.114454662786178</v>
       </c>
       <c r="E98">
-        <v>-44.47137888670306</v>
+        <v>-46.12644190606989</v>
       </c>
       <c r="F98">
-        <v>-4.216689268129402</v>
+        <v>-4.457524664982317</v>
       </c>
       <c r="G98">
-        <v>-11.70062439934286</v>
+        <v>-12.97836849026404</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.467887095747518</v>
       </c>
       <c r="E99">
-        <v>-47.84657432556563</v>
+        <v>-47.84204940182723</v>
       </c>
       <c r="F99">
-        <v>-4.352558089536577</v>
+        <v>-4.445659958672019</v>
       </c>
       <c r="G99">
-        <v>-12.03848346762342</v>
+        <v>-13.10725572923812</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.8161005077435222</v>
       </c>
       <c r="E100">
-        <v>-47.76078247753147</v>
+        <v>-49.12126237083953</v>
       </c>
       <c r="F100">
-        <v>-4.727990763833369</v>
+        <v>-4.507835559191344</v>
       </c>
       <c r="G100">
-        <v>-12.18931923637499</v>
+        <v>-13.48438300691362</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.2023329862055651</v>
       </c>
       <c r="E101">
-        <v>-50.5964487694252</v>
+        <v>-50.15601316806111</v>
       </c>
       <c r="F101">
-        <v>-4.548290538041863</v>
+        <v>-4.692417354087547</v>
       </c>
       <c r="G101">
-        <v>-12.72973683987396</v>
+        <v>-13.21677254871844</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>0.4165872692283811</v>
       </c>
       <c r="E102">
-        <v>-50.52024253312875</v>
+        <v>-52.02399991072075</v>
       </c>
       <c r="F102">
-        <v>-4.763500389289176</v>
+        <v>-4.783524514517048</v>
       </c>
       <c r="G102">
-        <v>-12.11423422193457</v>
+        <v>-13.50556397778132</v>
       </c>
     </row>
   </sheetData>
